--- a/feedback_surveys/021_storage_solutions_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/021_storage_solutions_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,8 +792,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,12 +821,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'file_server',_'value':_'file_server'}</t>
+          <t>file_server</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'File Server', 'value': 'File Server'}</t>
+          <t>File Server</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'nas',_'value':_'nas'}</t>
+          <t>nas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'NAS', 'value': 'NAS'}</t>
+          <t>NAS</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'san',_'value':_'san'}</t>
+          <t>san</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'SAN', 'value': 'SAN'}</t>
+          <t>SAN</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on-premise',_'value':_'on-premise'}</t>
+          <t>on-premise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On-premise', 'value': 'On-premise'}</t>
+          <t>On-premise</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cloud',_'value':_'cloud'}</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cloud', 'value': 'Cloud'}</t>
+          <t>Cloud</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'server',_'value':_'server'}</t>
+          <t>server</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Server', 'value': 'Server'}</t>
+          <t>Server</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'storage',_'value':_'storage'}</t>
+          <t>storage</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Storage', 'value': 'Storage'}</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rack',_'value':_'rack'}</t>
+          <t>rack</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rack', 'value': 'Rack'}</t>
+          <t>Rack</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'on-site',_'value':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'On-site', 'value': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'off-site',_'value':_'off-site'}</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Off-site', 'value': 'Off-site'}</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
